--- a/src/test/resources/data/DatosPROD.xlsx
+++ b/src/test/resources/data/DatosPROD.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automatización Whatsapp\Whatsapp\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA80D5A4-1450-4254-B3E0-0F55C5CBB49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EA3792-3540-44ED-A9D0-6E6933131390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{2593242D-A253-4AF1-956E-441BB7B64BAE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10920" activeTab="2" xr2:uid="{2593242D-A253-4AF1-956E-441BB7B64BAE}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="4" r:id="rId1"/>
     <sheet name="correo" sheetId="5" r:id="rId2"/>
-    <sheet name="Hoja1" sheetId="6" r:id="rId3"/>
+    <sheet name="Post" sheetId="7" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$F$1:$G$1</definedName>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
   <si>
     <t>opcionPaquete</t>
   </si>
@@ -153,189 +153,6 @@
     <t>numero</t>
   </si>
   <si>
-    <t>Paquetes todo incluido con redes</t>
-  </si>
-  <si>
-    <t>Todo incluido 30 Días con Minutos Ilimitados + 18GB</t>
-  </si>
-  <si>
-    <t>TipoPaquete</t>
-  </si>
-  <si>
-    <t>Paquete</t>
-  </si>
-  <si>
-    <t>Todo incluido 3 Días con Minutos Ilimitados + 400MB</t>
-  </si>
-  <si>
-    <t>Todo Incluido 50 minutos + SMS Ilimitados + W + 50 MB 1 Dia</t>
-  </si>
-  <si>
-    <t>Todo Incluido 6 Dias con Minutos Ilimitados + 1.4GB</t>
-  </si>
-  <si>
-    <t>Todo Incluido 7 Dias con Minutos Ilimitados + 2GB</t>
-  </si>
-  <si>
-    <t>Todo incluido 10 Dias con Minutos Ilimitados + 3.5GB</t>
-  </si>
-  <si>
-    <t>Todo incluido Voz Ilimitado + 80GB + WhatsApp Facebook Twitter,Vig 30 dias</t>
-  </si>
-  <si>
-    <t>Todo Incluido 20 Dias con Minutos Ilimitados + 7.5GB</t>
-  </si>
-  <si>
-    <t>Todo Incluido 30 Días con Minutos Ilimitados + 12GB</t>
-  </si>
-  <si>
-    <t>Paquetes todo incluido</t>
-  </si>
-  <si>
-    <t>Todo Incluido 7 Dias con Minutos Ilimitados 10GB No incluye redes</t>
-  </si>
-  <si>
-    <t>Todo Incluido 15 Dias con Minutos Ilimitados 20GB No incluye redes</t>
-  </si>
-  <si>
-    <t>Todo Incluido 30 Dias con Minutos Ilimitados 30GB No incluye redes</t>
-  </si>
-  <si>
-    <t>Paquetes de datos</t>
-  </si>
-  <si>
-    <t>Navegacion Ilimitada 2 horas</t>
-  </si>
-  <si>
-    <t>Navegación 200MB+WhatsApp 1 dia</t>
-  </si>
-  <si>
-    <t>Navegación 400MB+WhatsApp Facebook Twitter 1 dia</t>
-  </si>
-  <si>
-    <t>Navegación 800MB+WhatsApp Facebook Twitter 3 Días</t>
-  </si>
-  <si>
-    <t>Navegación 2GB+WhatsApp Facebook Twitter 7 Días</t>
-  </si>
-  <si>
-    <t>Paquetes apps</t>
-  </si>
-  <si>
-    <t>Paquete de WAZE por 1 Día</t>
-  </si>
-  <si>
-    <t>Paquete de Instagram 1 Día</t>
-  </si>
-  <si>
-    <t>Paquete de YouTube por 1 hora</t>
-  </si>
-  <si>
-    <t>Paquete de Waze por 7 dias</t>
-  </si>
-  <si>
-    <t>Chat WhatsApp por 15 días</t>
-  </si>
-  <si>
-    <t>Paquete de Instagram por 7 dias</t>
-  </si>
-  <si>
-    <t>Chat WhatsApp por 30 días</t>
-  </si>
-  <si>
-    <t>Paquetes de voz</t>
-  </si>
-  <si>
-    <t>Paquete 1000 Minutos</t>
-  </si>
-  <si>
-    <t>Paquetes Relevo comunidad sorda</t>
-  </si>
-  <si>
-    <t>Relevo SMS Ilimitados + WTF + 500MB 7 Dias</t>
-  </si>
-  <si>
-    <t>Relevo SMS Ilimitados + WTF + 1.5GB 15 Dias</t>
-  </si>
-  <si>
-    <t>Relevo SMS Ilimitados + WTF + 4GB 30 Dias</t>
-  </si>
-  <si>
-    <t>Paquetes Gaming</t>
-  </si>
-  <si>
-    <t>Todo Incluido Min y Sms Ilimitados + Free Fire + WFT + 2GB 7 Dias</t>
-  </si>
-  <si>
-    <t>Todo Incluido Min y Sms Ilimitados + Free Fire + WFT +500MB 2 Dias</t>
-  </si>
-  <si>
-    <t>precio</t>
-  </si>
-  <si>
-    <t>$3.000</t>
-  </si>
-  <si>
-    <t>$2.500</t>
-  </si>
-  <si>
-    <t>$9.000</t>
-  </si>
-  <si>
-    <t>$15.000</t>
-  </si>
-  <si>
-    <t>$1.500</t>
-  </si>
-  <si>
-    <t>$16.000</t>
-  </si>
-  <si>
-    <t>Paquete 300 Minutos</t>
-  </si>
-  <si>
-    <t>$2.000</t>
-  </si>
-  <si>
-    <t>$5.000</t>
-  </si>
-  <si>
-    <t>$10.000</t>
-  </si>
-  <si>
-    <t>$1.000</t>
-  </si>
-  <si>
-    <t>$18.000</t>
-  </si>
-  <si>
-    <t>$4.000</t>
-  </si>
-  <si>
-    <t>$7.000</t>
-  </si>
-  <si>
-    <t>$8.000</t>
-  </si>
-  <si>
-    <t>$11.000</t>
-  </si>
-  <si>
-    <t>$100.000</t>
-  </si>
-  <si>
-    <t>$21.000</t>
-  </si>
-  <si>
-    <t>$31.000</t>
-  </si>
-  <si>
-    <t>$41.000</t>
-  </si>
-  <si>
-    <t>$30.000</t>
-  </si>
-  <si>
     <t>saludo</t>
   </si>
   <si>
@@ -349,13 +166,16 @@
   </si>
   <si>
     <t>3558</t>
+  </si>
+  <si>
+    <t>numeroPost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,20 +211,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
@@ -431,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -454,132 +260,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -593,38 +279,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1242,24 +897,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>100</v>
+      <c r="A2" s="11" t="s">
+        <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>101</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1270,338 +925,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7959C7D7-2248-4959-811A-80A252B53B3D}">
-  <dimension ref="A1:C33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC0943B-5143-4833-AE8F-4E91CAAB95F2}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
-    <col min="2" max="2" width="73" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="3"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24"/>
-      <c r="B15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24"/>
-      <c r="B16" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-      <c r="B17" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
-      <c r="B18" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24"/>
-      <c r="B20" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="24"/>
-      <c r="B22" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="24"/>
-      <c r="B23" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24"/>
-      <c r="B24" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
-      <c r="B25" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24"/>
-      <c r="B27" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
-      <c r="B28" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24"/>
-      <c r="B30" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="20"/>
-      <c r="B31" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20"/>
-      <c r="B33" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>85</v>
+      <c r="B2">
+        <v>2840</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A31"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>